--- a/artifacts/ADA_USDT/metrics/ADA_USDT_metrics.xlsx
+++ b/artifacts/ADA_USDT/metrics/ADA_USDT_metrics.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003620618530290284</v>
+        <v>0.00318499312036369</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0601715757670537</v>
+        <v>0.05643574328706667</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03876763452895884</v>
+        <v>0.03508775788669716</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.921462085002908</v>
+        <v>0.887657931551306</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.023801329285787</v>
+        <v>4.410457182823066</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7684091304347827</v>
+        <v>0.7960811965811967</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7422305889749445</v>
+        <v>0.7792074371960271</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8350516919893617</v>
+        <v>0.8464949239780464</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8052675544547088</v>
+        <v>0.8315956500570049</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/ADA_USDT/metrics/ADA_USDT_metrics.xlsx
+++ b/artifacts/ADA_USDT/metrics/ADA_USDT_metrics.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00318499312036369</v>
+        <v>0.002851084321873623</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05643574328706667</v>
+        <v>0.05339554589920045</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03508775788669716</v>
+        <v>0.03228707875484523</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.887657931551306</v>
+        <v>0.8998387603147284</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.410457182823066</v>
+        <v>3.950250416421419</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7960811965811967</v>
+        <v>0.7958517094017094</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7792074371960271</v>
+        <v>0.7965597159700613</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8464949239780464</v>
+        <v>0.8462423364439069</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8315956500570049</v>
+        <v>0.8467923884788098</v>
       </c>
     </row>
   </sheetData>
